--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/250000/Output_21_23.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/250000/Output_21_23.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>419238.313943579</v>
+        <v>422543.5811569981</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11084306.15509253</v>
+        <v>11084373.30616851</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17470502.92572541</v>
+        <v>17470865.98181603</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5629580.373263204</v>
+        <v>5629365.807800127</v>
       </c>
     </row>
     <row r="11">
@@ -7959,22 +7959,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K2" t="n">
-        <v>212.9306450148298</v>
+        <v>214.0546037115793</v>
       </c>
       <c r="L2" t="n">
-        <v>226.8847868292837</v>
+        <v>228.2791569798279</v>
       </c>
       <c r="M2" t="n">
-        <v>220.4637106142074</v>
+        <v>222.0152160730528</v>
       </c>
       <c r="N2" t="n">
-        <v>219.3706314357869</v>
+        <v>220.9472418750055</v>
       </c>
       <c r="O2" t="n">
-        <v>220.6154275020887</v>
+        <v>222.1041760324343</v>
       </c>
       <c r="P2" t="n">
-        <v>223.1396590718525</v>
+        <v>224.4102714990878</v>
       </c>
       <c r="Q2" t="n">
         <v>212.3149906599047</v>
@@ -8035,28 +8035,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J3" t="n">
-        <v>123.9925889308176</v>
+        <v>124.4392452907996</v>
       </c>
       <c r="K3" t="n">
-        <v>132.9788163328496</v>
+        <v>133.742223194437</v>
       </c>
       <c r="L3" t="n">
-        <v>132.0159835534591</v>
+        <v>133.0424782891216</v>
       </c>
       <c r="M3" t="n">
-        <v>134.5040339220183</v>
+        <v>135.7019048619077</v>
       </c>
       <c r="N3" t="n">
-        <v>123.5097686871069</v>
+        <v>124.7393437063989</v>
       </c>
       <c r="O3" t="n">
-        <v>135.4315463312369</v>
+        <v>136.5563672569108</v>
       </c>
       <c r="P3" t="n">
-        <v>128.2241055275378</v>
+        <v>129.1268734863556</v>
       </c>
       <c r="Q3" t="n">
-        <v>136.1378495577196</v>
+        <v>136.7413260305349</v>
       </c>
       <c r="R3" t="n">
         <v>45.52166981132082</v>
@@ -8120,19 +8120,19 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L4" t="n">
-        <v>131.131299232058</v>
+        <v>131.7205602141891</v>
       </c>
       <c r="M4" t="n">
-        <v>134.9683741115395</v>
+        <v>135.5896671967106</v>
       </c>
       <c r="N4" t="n">
-        <v>123.8222329898233</v>
+        <v>124.4287531140874</v>
       </c>
       <c r="O4" t="n">
-        <v>134.8881450092198</v>
+        <v>135.4483645121045</v>
       </c>
       <c r="P4" t="n">
-        <v>134.6746269999673</v>
+        <v>135.0065633140411</v>
       </c>
       <c r="Q4" t="n">
         <v>65.34295837775146</v>
@@ -8193,28 +8193,28 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>101.8872713608571</v>
+        <v>100.9387195582597</v>
       </c>
       <c r="K5" t="n">
-        <v>101.4515796881966</v>
+        <v>100.0299464227919</v>
       </c>
       <c r="L5" t="n">
-        <v>88.58514863832892</v>
+        <v>86.82148686318186</v>
       </c>
       <c r="M5" t="n">
-        <v>66.57871563933304</v>
+        <v>64.61630209323863</v>
       </c>
       <c r="N5" t="n">
-        <v>62.99561636041</v>
+        <v>61.00144891149961</v>
       </c>
       <c r="O5" t="n">
-        <v>72.95493503977715</v>
+        <v>71.0718992657024</v>
       </c>
       <c r="P5" t="n">
-        <v>97.11484500150067</v>
+        <v>95.50771753390021</v>
       </c>
       <c r="Q5" t="n">
-        <v>121.5885441458063</v>
+        <v>120.3816583481039</v>
       </c>
       <c r="R5" t="n">
         <v>65.71641987298243</v>
@@ -8272,28 +8272,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J6" t="n">
-        <v>79.69128704402516</v>
+        <v>79.12633608862856</v>
       </c>
       <c r="K6" t="n">
-        <v>57.26083520077407</v>
+        <v>56.29524403393702</v>
       </c>
       <c r="L6" t="n">
-        <v>30.20381374213829</v>
+        <v>28.90545725697471</v>
       </c>
       <c r="M6" t="n">
-        <v>15.69403392201831</v>
+        <v>14.17891314335149</v>
       </c>
       <c r="N6" t="n">
-        <v>1.555221517295564</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>23.86696142557648</v>
+        <v>22.44423757443683</v>
       </c>
       <c r="P6" t="n">
-        <v>38.68369043319815</v>
+        <v>37.54182911310821</v>
       </c>
       <c r="Q6" t="n">
-        <v>76.28245333130452</v>
+        <v>75.51914927829571</v>
       </c>
       <c r="R6" t="n">
         <v>45.52166981132082</v>
@@ -8354,22 +8354,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K7" t="n">
-        <v>80.40735653119111</v>
+        <v>79.82491575659759</v>
       </c>
       <c r="L7" t="n">
-        <v>72.68585660910713</v>
+        <v>71.94053294496764</v>
       </c>
       <c r="M7" t="n">
-        <v>73.34584952137556</v>
+        <v>72.56001021962938</v>
       </c>
       <c r="N7" t="n">
-        <v>63.66495430129872</v>
+        <v>62.89780050171086</v>
       </c>
       <c r="O7" t="n">
-        <v>79.32316140266244</v>
+        <v>78.61457070130248</v>
       </c>
       <c r="P7" t="n">
-        <v>87.12918437701649</v>
+        <v>86.52286261917671</v>
       </c>
       <c r="Q7" t="n">
         <v>65.34295837775146</v>
@@ -8430,28 +8430,28 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>92.33364322015362</v>
+        <v>92.06191329280011</v>
       </c>
       <c r="K8" t="n">
-        <v>87.13316762789512</v>
+        <v>86.72591490550931</v>
       </c>
       <c r="L8" t="n">
-        <v>70.82189235692189</v>
+        <v>70.31665934305323</v>
       </c>
       <c r="M8" t="n">
-        <v>46.8136704132024</v>
+        <v>46.25150133729363</v>
       </c>
       <c r="N8" t="n">
-        <v>42.91075203880197</v>
+        <v>42.33948647951536</v>
       </c>
       <c r="O8" t="n">
-        <v>53.9893672005812</v>
+        <v>53.44993733213093</v>
       </c>
       <c r="P8" t="n">
-        <v>80.92817163466651</v>
+        <v>80.46778072209531</v>
       </c>
       <c r="Q8" t="n">
-        <v>109.4330265578666</v>
+        <v>109.0872921559756</v>
       </c>
       <c r="R8" t="n">
         <v>65.71641987298243</v>
@@ -8509,28 +8509,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J9" t="n">
-        <v>74.00121157232707</v>
+        <v>73.83937108913167</v>
       </c>
       <c r="K9" t="n">
-        <v>47.53558991775522</v>
+        <v>47.25897875440141</v>
       </c>
       <c r="L9" t="n">
-        <v>17.12702128930813</v>
+        <v>16.75508344424118</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4340339220183296</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>9.537565199161406</v>
+        <v>9.130000058643361</v>
       </c>
       <c r="P9" t="n">
-        <v>27.18308665961325</v>
+        <v>26.85597970277001</v>
       </c>
       <c r="Q9" t="n">
-        <v>68.59460427470074</v>
+        <v>68.37594193669796</v>
       </c>
       <c r="R9" t="n">
         <v>45.52166981132082</v>
@@ -8591,22 +8591,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K10" t="n">
-        <v>74.54112702299442</v>
+        <v>74.37427626277801</v>
       </c>
       <c r="L10" t="n">
-        <v>65.17910251074647</v>
+        <v>64.96559098237566</v>
       </c>
       <c r="M10" t="n">
-        <v>65.43102984924441</v>
+        <v>65.20591187910269</v>
       </c>
       <c r="N10" t="n">
-        <v>55.93833135047905</v>
+        <v>55.71856618250388</v>
       </c>
       <c r="O10" t="n">
-        <v>72.18637451741654</v>
+        <v>71.98338581476828</v>
       </c>
       <c r="P10" t="n">
-        <v>81.02243027865583</v>
+        <v>80.84873837615825</v>
       </c>
       <c r="Q10" t="n">
         <v>65.34295837775146</v>
@@ -8667,31 +8667,31 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>71.86158291864606</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K11" t="n">
-        <v>56.45085607010614</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L11" t="n">
-        <v>32.75777175390681</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M11" t="n">
-        <v>4.460002071493847</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>13.34886468801838</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P11" t="n">
-        <v>46.24244299145042</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q11" t="n">
-        <v>83.38548886942436</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R11" t="n">
-        <v>65.71641987298244</v>
+        <v>65.71641987298243</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -8746,10 +8746,10 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J12" t="n">
-        <v>61.80819270440252</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K12" t="n">
-        <v>26.69577859700048</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -8764,10 +8764,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.538935716217026</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q12" t="n">
-        <v>52.12064201054979</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R12" t="n">
         <v>45.52166981132082</v>
@@ -8825,25 +8825,25 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>33.63624132272332</v>
+        <v>33.63624132272333</v>
       </c>
       <c r="K13" t="n">
-        <v>61.9706352197157</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L13" t="n">
-        <v>49.0932008714022</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M13" t="n">
-        <v>48.47070198039195</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N13" t="n">
-        <v>39.38128217015117</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O13" t="n">
-        <v>56.89325976331817</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P13" t="n">
-        <v>67.93652863931156</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q13" t="n">
         <v>65.34295837775146</v>
@@ -8904,28 +8904,28 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>71.86158291864606</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K14" t="n">
-        <v>56.45085607010614</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L14" t="n">
-        <v>32.75777175390681</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M14" t="n">
-        <v>4.46000207149379</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>13.34886468801838</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P14" t="n">
-        <v>46.24244299145042</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q14" t="n">
-        <v>83.38548886942436</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R14" t="n">
         <v>65.71641987298243</v>
@@ -8983,10 +8983,10 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J15" t="n">
-        <v>61.80819270440254</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K15" t="n">
-        <v>26.69577859700048</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -9001,13 +9001,13 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.538935716216997</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q15" t="n">
-        <v>52.1206420105498</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R15" t="n">
-        <v>45.52166981132083</v>
+        <v>45.52166981132082</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -9062,25 +9062,25 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>33.63624132272334</v>
+        <v>33.63624132272333</v>
       </c>
       <c r="K16" t="n">
-        <v>61.9706352197157</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L16" t="n">
-        <v>49.0932008714022</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M16" t="n">
-        <v>48.47070198039195</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N16" t="n">
-        <v>39.38128217015117</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O16" t="n">
-        <v>56.89325976331817</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P16" t="n">
-        <v>67.93652863931156</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q16" t="n">
         <v>65.34295837775146</v>
@@ -9141,31 +9141,31 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>71.86158291864606</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K17" t="n">
-        <v>56.45085607010614</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L17" t="n">
-        <v>32.75777175390681</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M17" t="n">
-        <v>4.46000207149379</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>13.34886468801838</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P17" t="n">
-        <v>46.24244299145042</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q17" t="n">
-        <v>83.38548886942436</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R17" t="n">
-        <v>65.71641987298244</v>
+        <v>65.71641987298243</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -9220,10 +9220,10 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J18" t="n">
-        <v>61.80819270440254</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K18" t="n">
-        <v>26.69577859700048</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -9238,10 +9238,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.538935716216997</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q18" t="n">
-        <v>52.1206420105498</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R18" t="n">
         <v>45.52166981132082</v>
@@ -9302,25 +9302,25 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K19" t="n">
-        <v>61.9706352197157</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L19" t="n">
-        <v>49.0932008714022</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M19" t="n">
-        <v>48.47070198039195</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N19" t="n">
-        <v>39.38128217015117</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O19" t="n">
-        <v>56.89325976331817</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P19" t="n">
-        <v>67.93652863931156</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q19" t="n">
-        <v>65.34295837775144</v>
+        <v>65.34295837775146</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -9378,28 +9378,28 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>71.86158291864606</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K20" t="n">
-        <v>56.45085607010614</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L20" t="n">
-        <v>32.75777175390681</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M20" t="n">
-        <v>4.46000207149379</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>13.34886468801838</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P20" t="n">
-        <v>46.24244299145042</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q20" t="n">
-        <v>83.38548886942436</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R20" t="n">
         <v>65.71641987298243</v>
@@ -9457,10 +9457,10 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J21" t="n">
-        <v>61.80819270440252</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K21" t="n">
-        <v>26.69577859700048</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -9475,13 +9475,13 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.538935716216997</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q21" t="n">
-        <v>52.1206420105498</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R21" t="n">
-        <v>45.52166981132083</v>
+        <v>45.52166981132082</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -9536,25 +9536,25 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>33.63624132272334</v>
+        <v>33.63624132272333</v>
       </c>
       <c r="K22" t="n">
-        <v>61.9706352197157</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L22" t="n">
-        <v>49.0932008714022</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M22" t="n">
-        <v>48.47070198039195</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N22" t="n">
-        <v>39.38128217015117</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O22" t="n">
-        <v>56.89325976331817</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P22" t="n">
-        <v>67.93652863931156</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q22" t="n">
         <v>65.34295837775146</v>
@@ -9615,31 +9615,31 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>71.86158291864606</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K23" t="n">
-        <v>56.45085607010614</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L23" t="n">
-        <v>32.75777175390675</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M23" t="n">
-        <v>4.460002071493631</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>13.34886468801832</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P23" t="n">
-        <v>46.24244299145042</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q23" t="n">
-        <v>83.38548886942436</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R23" t="n">
-        <v>65.71641987298244</v>
+        <v>65.71641987298243</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -9694,10 +9694,10 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J24" t="n">
-        <v>61.80819270440252</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K24" t="n">
-        <v>26.69577859700047</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -9712,10 +9712,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.538935716217054</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q24" t="n">
-        <v>52.12064201054979</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9773,25 +9773,25 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>33.63624132272332</v>
+        <v>33.63624132272333</v>
       </c>
       <c r="K25" t="n">
-        <v>61.97063521971572</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L25" t="n">
-        <v>49.0932008714022</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M25" t="n">
-        <v>48.47070198039195</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N25" t="n">
-        <v>39.38128217015115</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O25" t="n">
-        <v>56.89325976331817</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P25" t="n">
-        <v>67.93652863931173</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q25" t="n">
         <v>65.34295837775146</v>
@@ -9852,28 +9852,28 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>71.86158291864606</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K26" t="n">
-        <v>56.45085607010614</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L26" t="n">
-        <v>32.7577717539058</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M26" t="n">
-        <v>4.46000207149379</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>13.34886468801832</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P26" t="n">
-        <v>46.24244299145042</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q26" t="n">
-        <v>83.38548886942436</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R26" t="n">
         <v>65.71641987298243</v>
@@ -9931,10 +9931,10 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J27" t="n">
-        <v>61.80819270440252</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K27" t="n">
-        <v>26.69577859700047</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -9949,13 +9949,13 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.538935716216997</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q27" t="n">
-        <v>52.12064201054979</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R27" t="n">
-        <v>45.52166981132083</v>
+        <v>45.52166981132082</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -10010,25 +10010,25 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>33.63624132272334</v>
+        <v>33.63624132272333</v>
       </c>
       <c r="K28" t="n">
-        <v>61.97063521971572</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L28" t="n">
-        <v>49.0932008714022</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M28" t="n">
-        <v>48.47070198039195</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N28" t="n">
-        <v>39.38128217015115</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O28" t="n">
-        <v>56.89325976331817</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P28" t="n">
-        <v>67.93652863931158</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q28" t="n">
         <v>65.34295837775146</v>
@@ -10089,28 +10089,28 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>71.86158291864606</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K29" t="n">
-        <v>56.45085607010614</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L29" t="n">
-        <v>32.75777175390675</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M29" t="n">
-        <v>4.460002071493876</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>13.34886468801832</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P29" t="n">
-        <v>46.24244299145042</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q29" t="n">
-        <v>83.38548886942436</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R29" t="n">
         <v>65.71641987298243</v>
@@ -10168,10 +10168,10 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J30" t="n">
-        <v>61.80819270440252</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K30" t="n">
-        <v>26.69577859700047</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -10186,13 +10186,13 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.538935716216997</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q30" t="n">
-        <v>52.12064201054979</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R30" t="n">
-        <v>45.52166981132083</v>
+        <v>45.52166981132082</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -10247,25 +10247,25 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>33.63624132272334</v>
+        <v>33.63624132272333</v>
       </c>
       <c r="K31" t="n">
-        <v>61.97063521971572</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L31" t="n">
-        <v>49.0932008714022</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M31" t="n">
-        <v>48.47070198039195</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N31" t="n">
-        <v>39.38128217015115</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O31" t="n">
-        <v>56.89325976331817</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P31" t="n">
-        <v>67.93652863931172</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q31" t="n">
         <v>65.34295837775146</v>
@@ -10326,31 +10326,31 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>71.86158291864606</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K32" t="n">
-        <v>56.45085607010617</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L32" t="n">
-        <v>32.75777175390681</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M32" t="n">
-        <v>4.46000207149379</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>13.34886468801832</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P32" t="n">
-        <v>46.24244299145045</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q32" t="n">
-        <v>83.38548886942436</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R32" t="n">
-        <v>65.71641987298244</v>
+        <v>65.71641987298243</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -10405,10 +10405,10 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J33" t="n">
-        <v>61.80819270440253</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K33" t="n">
-        <v>26.6957785970005</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -10423,10 +10423,10 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.538935716216997</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q33" t="n">
-        <v>52.1206420105498</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R33" t="n">
         <v>45.52166981132082</v>
@@ -10484,25 +10484,25 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>33.63624132272332</v>
+        <v>33.63624132272333</v>
       </c>
       <c r="K34" t="n">
-        <v>61.97063521971573</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L34" t="n">
-        <v>49.09320087140222</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M34" t="n">
-        <v>48.47070198039196</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N34" t="n">
-        <v>39.38128217015117</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O34" t="n">
-        <v>56.89325976331818</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P34" t="n">
-        <v>67.93652863931159</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q34" t="n">
         <v>65.34295837775146</v>
@@ -10563,28 +10563,28 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>71.86158291864606</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K35" t="n">
-        <v>56.45085607010617</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L35" t="n">
-        <v>32.75777175390681</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M35" t="n">
-        <v>4.46000207149379</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>13.34886468801832</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P35" t="n">
-        <v>46.24244299145045</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q35" t="n">
-        <v>83.38548886942436</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R35" t="n">
         <v>65.71641987298243</v>
@@ -10642,10 +10642,10 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J36" t="n">
-        <v>61.80819270440253</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K36" t="n">
-        <v>26.6957785970005</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -10660,13 +10660,13 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.538935716216997</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q36" t="n">
-        <v>52.1206420105498</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R36" t="n">
-        <v>45.52166981132083</v>
+        <v>45.52166981132082</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -10721,25 +10721,25 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>33.63624132272334</v>
+        <v>33.63624132272333</v>
       </c>
       <c r="K37" t="n">
-        <v>61.97063521971573</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L37" t="n">
-        <v>49.09320087140222</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M37" t="n">
-        <v>48.47070198039196</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N37" t="n">
-        <v>39.38128217015117</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O37" t="n">
-        <v>56.89325976331818</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P37" t="n">
-        <v>67.93652863931159</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q37" t="n">
         <v>65.34295837775146</v>
@@ -10800,31 +10800,31 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>71.86158291864606</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K38" t="n">
-        <v>56.45085607010617</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L38" t="n">
-        <v>32.75777175390681</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M38" t="n">
-        <v>4.46000207149379</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>13.34886468801832</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P38" t="n">
-        <v>46.24244299145045</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q38" t="n">
-        <v>83.38548886942436</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R38" t="n">
-        <v>65.71641987298244</v>
+        <v>65.71641987298243</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -10879,10 +10879,10 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J39" t="n">
-        <v>61.80819270440253</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K39" t="n">
-        <v>26.6957785970005</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -10897,10 +10897,10 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.538935716216997</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q39" t="n">
-        <v>52.1206420105498</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R39" t="n">
         <v>45.52166981132082</v>
@@ -10961,25 +10961,25 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K40" t="n">
-        <v>61.97063521971573</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L40" t="n">
-        <v>49.09320087140222</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M40" t="n">
-        <v>48.47070198039196</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N40" t="n">
-        <v>39.38128217015117</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O40" t="n">
-        <v>56.89325976331818</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P40" t="n">
-        <v>67.93652863931159</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q40" t="n">
-        <v>65.34295837775144</v>
+        <v>65.34295837775146</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -11037,28 +11037,28 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>71.86158291864606</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K41" t="n">
-        <v>56.45085607010617</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L41" t="n">
-        <v>32.75777175390681</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M41" t="n">
-        <v>4.46000207149379</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>13.34886468801832</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P41" t="n">
-        <v>46.24244299145045</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q41" t="n">
-        <v>83.38548886942436</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R41" t="n">
         <v>65.71641987298243</v>
@@ -11116,10 +11116,10 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J42" t="n">
-        <v>61.80819270440253</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K42" t="n">
-        <v>26.6957785970005</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -11134,10 +11134,10 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.538935716216997</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q42" t="n">
-        <v>52.1206420105498</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -11195,25 +11195,25 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>33.63624132272332</v>
+        <v>33.63624132272333</v>
       </c>
       <c r="K43" t="n">
-        <v>61.97063521971573</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L43" t="n">
-        <v>49.09320087140222</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M43" t="n">
-        <v>48.47070198039196</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N43" t="n">
-        <v>39.38128217015117</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O43" t="n">
-        <v>56.89325976331818</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P43" t="n">
-        <v>67.93652863931159</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q43" t="n">
         <v>65.34295837775146</v>
@@ -11274,28 +11274,28 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>71.86158291864606</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K44" t="n">
-        <v>56.45085607010617</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L44" t="n">
-        <v>32.75777175390681</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M44" t="n">
-        <v>4.46000207149379</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>13.34886468801832</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P44" t="n">
-        <v>46.24244299145045</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q44" t="n">
-        <v>83.38548886942436</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R44" t="n">
         <v>65.71641987298243</v>
@@ -11353,10 +11353,10 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J45" t="n">
-        <v>61.80819270440253</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K45" t="n">
-        <v>26.6957785970005</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -11371,10 +11371,10 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.538935716216997</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q45" t="n">
-        <v>52.1206420105498</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R45" t="n">
         <v>45.52166981132082</v>
@@ -11435,25 +11435,25 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K46" t="n">
-        <v>61.97063521971573</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L46" t="n">
-        <v>49.09320087140222</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M46" t="n">
-        <v>48.47070198039196</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N46" t="n">
-        <v>39.38128217015117</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O46" t="n">
-        <v>56.89325976331818</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P46" t="n">
-        <v>67.93652863931159</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q46" t="n">
-        <v>65.34295837775144</v>
+        <v>65.34295837775146</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -22516,16 +22516,16 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>6.876045741711209</v>
+        <v>6.876045741711437</v>
       </c>
       <c r="G2" t="n">
-        <v>15.24645610809965</v>
+        <v>15.25529200088408</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>2.220446049250313e-15</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -22552,16 +22552,16 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>5.773159728050814e-15</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>5.717648576819556e-15</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>8.792445937988447e-15</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -22598,10 +22598,10 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>4.357625371653739e-15</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>6.106226635438361e-15</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -22634,13 +22634,13 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>7.438494264988549e-15</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>1.063038546078587e-14</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.374855090885418e-14</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -22677,7 +22677,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>7.327471962526033e-15</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -22710,16 +22710,16 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3.33066907387547e-15</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.387778780781446e-15</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.055148586033173e-14</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -22753,10 +22753,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>6.876045741711323</v>
+        <v>6.876045741711437</v>
       </c>
       <c r="G5" t="n">
-        <v>14.37007419855202</v>
+        <v>14.3588981658848</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -22789,16 +22789,16 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>8.881784197001252e-15</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.17128529097954e-14</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -22905,7 +22905,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1.193711796076968e-12</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -22917,13 +22917,13 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1.06581410364015e-14</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -22947,16 +22947,16 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.06581410364015e-14</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.154631945610163e-14</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>4.662936703425657e-15</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.574781971491745e-14</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -22990,10 +22990,10 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>6.876045741711323</v>
+        <v>6.876045741711437</v>
       </c>
       <c r="G8" t="n">
-        <v>14.25751138448167</v>
+        <v>14.25430980652214</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -23026,7 +23026,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -23035,7 +23035,7 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>8.604228440844963e-16</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -23108,10 +23108,10 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.243449787580175e-14</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -23136,7 +23136,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.842170943040401e-12</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -23151,10 +23151,10 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1.015854067532018e-14</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.664535259100376e-15</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -23184,16 +23184,16 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1.287858708565182e-14</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>3.469446951953614e-18</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -23230,13 +23230,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G11" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H11" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I11" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -23263,16 +23263,16 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>69.06027372004411</v>
+        <v>69.10542099048568</v>
       </c>
       <c r="S11" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T11" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U11" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V11" t="n">
         <v>327.7522584701349</v>
@@ -23309,13 +23309,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G12" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H12" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I12" t="n">
-        <v>65.6985196438679</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -23342,16 +23342,16 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>57.42273981302047</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S12" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T12" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U12" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V12" t="n">
         <v>232.8005871494253</v>
@@ -23388,16 +23388,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G13" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H13" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I13" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J13" t="n">
-        <v>52.56180306749245</v>
+        <v>52.58459624356988</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -23418,19 +23418,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>37.84204325169436</v>
+        <v>37.86903925848996</v>
       </c>
       <c r="R13" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S13" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T13" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U13" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V13" t="n">
         <v>252.137643323828</v>
@@ -23467,13 +23467,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G14" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H14" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I14" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -23500,16 +23500,16 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>69.06027372004418</v>
+        <v>69.10542099048568</v>
       </c>
       <c r="S14" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T14" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U14" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V14" t="n">
         <v>327.7522584701349</v>
@@ -23546,13 +23546,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G15" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H15" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I15" t="n">
-        <v>65.69851964386791</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -23579,16 +23579,16 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>57.42273981302048</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S15" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T15" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U15" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V15" t="n">
         <v>232.8005871494253</v>
@@ -23625,16 +23625,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G16" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H16" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I16" t="n">
-        <v>138.0970323043075</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J16" t="n">
-        <v>52.56180306749245</v>
+        <v>52.58459624356988</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -23655,19 +23655,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>37.84204325169439</v>
+        <v>37.86903925848996</v>
       </c>
       <c r="R16" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S16" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T16" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U16" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V16" t="n">
         <v>252.137643323828</v>
@@ -23704,13 +23704,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G17" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H17" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I17" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -23737,16 +23737,16 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>69.06027372004417</v>
+        <v>69.10542099048568</v>
       </c>
       <c r="S17" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T17" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U17" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V17" t="n">
         <v>327.7522584701349</v>
@@ -23783,13 +23783,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G18" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H18" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I18" t="n">
-        <v>65.69851964386791</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -23816,16 +23816,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>57.42273981302048</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S18" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T18" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U18" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V18" t="n">
         <v>232.8005871494253</v>
@@ -23862,16 +23862,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G19" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H19" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I19" t="n">
-        <v>138.0970323043075</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J19" t="n">
-        <v>52.56180306749246</v>
+        <v>52.58459624356988</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -23892,19 +23892,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>37.84204325169441</v>
+        <v>37.86903925848996</v>
       </c>
       <c r="R19" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S19" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T19" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U19" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V19" t="n">
         <v>252.137643323828</v>
@@ -23941,13 +23941,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G20" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H20" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I20" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -23974,16 +23974,16 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>69.06027372004418</v>
+        <v>69.10542099048568</v>
       </c>
       <c r="S20" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T20" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U20" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V20" t="n">
         <v>327.7522584701349</v>
@@ -24020,13 +24020,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G21" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H21" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I21" t="n">
-        <v>65.69851964386791</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -24053,16 +24053,16 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>57.42273981302048</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S21" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T21" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U21" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V21" t="n">
         <v>232.8005871494253</v>
@@ -24099,16 +24099,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G22" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H22" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I22" t="n">
-        <v>138.0970323043075</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J22" t="n">
-        <v>52.56180306749245</v>
+        <v>52.58459624356988</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -24129,19 +24129,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>37.84204325169439</v>
+        <v>37.86903925848996</v>
       </c>
       <c r="R22" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S22" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T22" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U22" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V22" t="n">
         <v>252.137643323828</v>
@@ -24178,13 +24178,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G23" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H23" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I23" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -24196,7 +24196,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.589839371263224e-13</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -24211,16 +24211,16 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>69.06027372004411</v>
+        <v>69.10542099048568</v>
       </c>
       <c r="S23" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T23" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U23" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V23" t="n">
         <v>327.7522584701349</v>
@@ -24257,13 +24257,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G24" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H24" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I24" t="n">
-        <v>65.6985196438679</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -24290,16 +24290,16 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>57.42273981302047</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S24" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T24" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U24" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V24" t="n">
         <v>232.8005871494253</v>
@@ -24336,16 +24336,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G25" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H25" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I25" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J25" t="n">
-        <v>52.56180306749246</v>
+        <v>52.58459624356988</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -24366,19 +24366,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>37.84204325169438</v>
+        <v>37.86903925848996</v>
       </c>
       <c r="R25" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S25" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T25" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U25" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V25" t="n">
         <v>252.137643323828</v>
@@ -24415,13 +24415,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G26" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H26" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I26" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -24430,7 +24430,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>9.521272659185342e-13</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -24448,16 +24448,16 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>69.06027372004412</v>
+        <v>69.10542099048568</v>
       </c>
       <c r="S26" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T26" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U26" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V26" t="n">
         <v>327.7522584701349</v>
@@ -24494,13 +24494,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G27" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H27" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I27" t="n">
-        <v>65.6985196438679</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -24527,16 +24527,16 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>57.42273981302046</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S27" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T27" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U27" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V27" t="n">
         <v>232.8005871494253</v>
@@ -24573,16 +24573,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G28" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H28" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I28" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J28" t="n">
-        <v>52.56180306749245</v>
+        <v>52.58459624356988</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -24603,19 +24603,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>37.84204325169438</v>
+        <v>37.86903925848996</v>
       </c>
       <c r="R28" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S28" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T28" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U28" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V28" t="n">
         <v>252.137643323828</v>
@@ -24652,13 +24652,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G29" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H29" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I29" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -24685,16 +24685,16 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>69.06027372004412</v>
+        <v>69.10542099048568</v>
       </c>
       <c r="S29" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T29" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U29" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V29" t="n">
         <v>327.7522584701349</v>
@@ -24731,13 +24731,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G30" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H30" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I30" t="n">
-        <v>65.6985196438679</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -24764,16 +24764,16 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>57.42273981302046</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S30" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T30" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U30" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V30" t="n">
         <v>232.8005871494253</v>
@@ -24810,16 +24810,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G31" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H31" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I31" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J31" t="n">
-        <v>52.56180306749245</v>
+        <v>52.58459624356988</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -24840,19 +24840,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>37.84204325169438</v>
+        <v>37.86903925848996</v>
       </c>
       <c r="R31" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S31" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T31" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U31" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V31" t="n">
         <v>252.137643323828</v>
@@ -24889,13 +24889,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G32" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H32" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I32" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -24922,16 +24922,16 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>69.06027372004414</v>
+        <v>69.10542099048568</v>
       </c>
       <c r="S32" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T32" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U32" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V32" t="n">
         <v>327.7522584701349</v>
@@ -24968,13 +24968,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H33" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I33" t="n">
-        <v>65.6985196438679</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -25001,16 +25001,16 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>57.42273981302047</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S33" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T33" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U33" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V33" t="n">
         <v>232.8005871494253</v>
@@ -25047,16 +25047,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G34" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H34" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I34" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J34" t="n">
-        <v>52.56180306749246</v>
+        <v>52.58459624356988</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -25077,19 +25077,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>37.84204325169439</v>
+        <v>37.86903925848996</v>
       </c>
       <c r="R34" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S34" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T34" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U34" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V34" t="n">
         <v>252.137643323828</v>
@@ -25126,13 +25126,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G35" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H35" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I35" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -25159,16 +25159,16 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>69.06027372004415</v>
+        <v>69.10542099048568</v>
       </c>
       <c r="S35" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T35" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U35" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V35" t="n">
         <v>327.7522584701349</v>
@@ -25205,13 +25205,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G36" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H36" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I36" t="n">
-        <v>65.6985196438679</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -25238,16 +25238,16 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>57.42273981302046</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S36" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T36" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U36" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V36" t="n">
         <v>232.8005871494253</v>
@@ -25284,16 +25284,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G37" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H37" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I37" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J37" t="n">
-        <v>52.56180306749245</v>
+        <v>52.58459624356988</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -25314,19 +25314,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>37.84204325169439</v>
+        <v>37.86903925848996</v>
       </c>
       <c r="R37" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S37" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T37" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U37" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V37" t="n">
         <v>252.137643323828</v>
@@ -25363,13 +25363,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G38" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H38" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I38" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -25396,16 +25396,16 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>69.06027372004414</v>
+        <v>69.10542099048568</v>
       </c>
       <c r="S38" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T38" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U38" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V38" t="n">
         <v>327.7522584701349</v>
@@ -25442,13 +25442,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G39" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H39" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I39" t="n">
-        <v>65.6985196438679</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -25475,16 +25475,16 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>57.42273981302047</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S39" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T39" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U39" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V39" t="n">
         <v>232.8005871494253</v>
@@ -25521,16 +25521,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G40" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H40" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I40" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J40" t="n">
-        <v>52.56180306749246</v>
+        <v>52.58459624356988</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -25551,19 +25551,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>37.84204325169441</v>
+        <v>37.86903925848996</v>
       </c>
       <c r="R40" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S40" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T40" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U40" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V40" t="n">
         <v>252.137643323828</v>
@@ -25600,13 +25600,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G41" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H41" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I41" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -25633,16 +25633,16 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>69.06027372004415</v>
+        <v>69.10542099048568</v>
       </c>
       <c r="S41" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T41" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U41" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V41" t="n">
         <v>327.7522584701349</v>
@@ -25679,13 +25679,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G42" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H42" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I42" t="n">
-        <v>65.6985196438679</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -25712,16 +25712,16 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>57.42273981302047</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S42" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T42" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U42" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V42" t="n">
         <v>232.8005871494253</v>
@@ -25758,16 +25758,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G43" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H43" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I43" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J43" t="n">
-        <v>52.56180306749246</v>
+        <v>52.58459624356988</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -25788,19 +25788,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>37.84204325169439</v>
+        <v>37.86903925848996</v>
       </c>
       <c r="R43" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S43" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T43" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U43" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V43" t="n">
         <v>252.137643323828</v>
@@ -25837,13 +25837,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G44" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H44" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I44" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -25870,16 +25870,16 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>69.06027372004415</v>
+        <v>69.10542099048568</v>
       </c>
       <c r="S44" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T44" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U44" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V44" t="n">
         <v>327.7522584701349</v>
@@ -25916,13 +25916,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G45" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H45" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I45" t="n">
-        <v>65.6985196438679</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -25949,16 +25949,16 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>57.42273981302047</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S45" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T45" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U45" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V45" t="n">
         <v>232.8005871494253</v>
@@ -25995,16 +25995,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G46" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H46" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I46" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J46" t="n">
-        <v>52.56180306749246</v>
+        <v>52.58459624356988</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -26025,19 +26025,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>37.84204325169441</v>
+        <v>37.86903925848996</v>
       </c>
       <c r="R46" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S46" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T46" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U46" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V46" t="n">
         <v>252.137643323828</v>
@@ -26078,7 +26078,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1072087.508989183</v>
+        <v>1072634.485728598</v>
       </c>
     </row>
     <row r="3">
@@ -26086,7 +26086,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1010719.779898986</v>
+        <v>1009928.175175978</v>
       </c>
     </row>
     <row r="4">
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1003060.950921126</v>
+        <v>1002844.098649911</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>306356.1175282692</v>
+        <v>306379.1793754585</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>306356.1175282692</v>
+        <v>306379.1793754585</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>306356.1175282692</v>
+        <v>306379.1793754585</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>306356.1175282692</v>
+        <v>306379.1793754585</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>306356.1175282691</v>
+        <v>306379.1793754585</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>306356.117528269</v>
+        <v>306379.1793754585</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>306356.1175282692</v>
+        <v>306379.1793754585</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>306356.1175282692</v>
+        <v>306379.1793754585</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>306356.1175282692</v>
+        <v>306379.1793754585</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>306356.1175282692</v>
+        <v>306379.1793754585</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>306356.1175282692</v>
+        <v>306379.1793754585</v>
       </c>
     </row>
     <row r="16">
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>306356.1175282692</v>
+        <v>306379.1793754585</v>
       </c>
     </row>
   </sheetData>
@@ -26261,49 +26261,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>471086.4707622972</v>
+        <v>471086.0663434843</v>
       </c>
       <c r="C2" t="n">
-        <v>471126.5827622972</v>
+        <v>471127.0942893123</v>
       </c>
       <c r="D2" t="n">
-        <v>471131.7347622972</v>
+        <v>471131.8812985204</v>
       </c>
       <c r="E2" t="n">
-        <v>137493.7336563085</v>
+        <v>137486.7539442033</v>
       </c>
       <c r="F2" t="n">
-        <v>137493.7336563085</v>
+        <v>137486.7539442033</v>
       </c>
       <c r="G2" t="n">
-        <v>137493.7336563085</v>
+        <v>137486.7539442033</v>
       </c>
       <c r="H2" t="n">
-        <v>137493.7336563086</v>
+        <v>137486.7539442033</v>
       </c>
       <c r="I2" t="n">
-        <v>137493.7336563086</v>
+        <v>137486.7539442033</v>
       </c>
       <c r="J2" t="n">
-        <v>137493.7336563085</v>
+        <v>137486.7539442033</v>
       </c>
       <c r="K2" t="n">
-        <v>137493.7336563086</v>
+        <v>137486.7539442033</v>
       </c>
       <c r="L2" t="n">
-        <v>137493.7336563086</v>
+        <v>137486.7539442033</v>
       </c>
       <c r="M2" t="n">
-        <v>137493.7336563085</v>
+        <v>137486.7539442033</v>
       </c>
       <c r="N2" t="n">
-        <v>137493.7336563085</v>
+        <v>137486.7539442033</v>
       </c>
       <c r="O2" t="n">
-        <v>137493.7336563085</v>
+        <v>137486.7539442033</v>
       </c>
       <c r="P2" t="n">
-        <v>137493.7336563085</v>
+        <v>137486.7539442033</v>
       </c>
     </row>
     <row r="3">
@@ -26313,16 +26313,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13490.582</v>
+        <v>11372.6296880741</v>
       </c>
       <c r="C3" t="n">
-        <v>198511.236</v>
+        <v>203044.182210827</v>
       </c>
       <c r="D3" t="n">
-        <v>23979.592</v>
+        <v>22280.77012981693</v>
       </c>
       <c r="E3" t="n">
-        <v>48204.18</v>
+        <v>47420.72226727413</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>453196.4634447009</v>
+        <v>452825.7486769923</v>
       </c>
       <c r="C4" t="n">
-        <v>382569.894104808</v>
+        <v>381202.731793032</v>
       </c>
       <c r="D4" t="n">
-        <v>373820.5655308232</v>
+        <v>373175.6561023303</v>
       </c>
       <c r="E4" t="n">
-        <v>25390.66179581224</v>
+        <v>25176.19445408718</v>
       </c>
       <c r="F4" t="n">
-        <v>25390.66179581223</v>
+        <v>25176.19445408718</v>
       </c>
       <c r="G4" t="n">
-        <v>25390.66179581223</v>
+        <v>25176.19445408718</v>
       </c>
       <c r="H4" t="n">
-        <v>25390.66179581223</v>
+        <v>25176.19445408718</v>
       </c>
       <c r="I4" t="n">
-        <v>25390.66179581222</v>
+        <v>25176.19445408718</v>
       </c>
       <c r="J4" t="n">
-        <v>25390.66179581219</v>
+        <v>25176.19445408718</v>
       </c>
       <c r="K4" t="n">
-        <v>25390.66179581223</v>
+        <v>25176.19445408718</v>
       </c>
       <c r="L4" t="n">
-        <v>25390.66179581224</v>
+        <v>25176.19445408718</v>
       </c>
       <c r="M4" t="n">
-        <v>25390.66179581224</v>
+        <v>25176.19445408718</v>
       </c>
       <c r="N4" t="n">
-        <v>25390.66179581224</v>
+        <v>25176.19445408718</v>
       </c>
       <c r="O4" t="n">
-        <v>25390.66179581224</v>
+        <v>25176.19445408718</v>
       </c>
       <c r="P4" t="n">
-        <v>25390.66179581224</v>
+        <v>25176.19445408718</v>
       </c>
     </row>
     <row r="5">
@@ -26417,49 +26417,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>33932.8</v>
+        <v>33884.88516240443</v>
       </c>
       <c r="C5" t="n">
-        <v>38685.2</v>
+        <v>38745.80483114667</v>
       </c>
       <c r="D5" t="n">
-        <v>39295.6</v>
+        <v>39312.96135688073</v>
       </c>
       <c r="E5" t="n">
-        <v>6976</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="F5" t="n">
-        <v>6976</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="G5" t="n">
-        <v>6976</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="H5" t="n">
-        <v>6976</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="I5" t="n">
-        <v>6976</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="J5" t="n">
-        <v>6976</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="K5" t="n">
-        <v>6976</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="L5" t="n">
-        <v>6976</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="M5" t="n">
-        <v>6976</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="N5" t="n">
-        <v>6976</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="O5" t="n">
-        <v>6976</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="P5" t="n">
-        <v>6976</v>
+        <v>6972.102563257328</v>
       </c>
     </row>
     <row r="6">
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-29533.37468240376</v>
+        <v>-26997.19718398646</v>
       </c>
       <c r="C6" t="n">
-        <v>-148639.7473425108</v>
+        <v>-151865.6245456934</v>
       </c>
       <c r="D6" t="n">
-        <v>34035.97723147399</v>
+        <v>36362.49370949249</v>
       </c>
       <c r="E6" t="n">
-        <v>56922.8918604963</v>
+        <v>57917.73465958464</v>
       </c>
       <c r="F6" t="n">
-        <v>105127.0718604963</v>
+        <v>105338.4569268588</v>
       </c>
       <c r="G6" t="n">
-        <v>105127.0718604963</v>
+        <v>105338.4569268588</v>
       </c>
       <c r="H6" t="n">
-        <v>105127.0718604963</v>
+        <v>105338.4569268588</v>
       </c>
       <c r="I6" t="n">
-        <v>105127.0718604963</v>
+        <v>105338.4569268588</v>
       </c>
       <c r="J6" t="n">
-        <v>105127.0718604963</v>
+        <v>105338.4569268588</v>
       </c>
       <c r="K6" t="n">
-        <v>105127.0718604963</v>
+        <v>105338.4569268588</v>
       </c>
       <c r="L6" t="n">
-        <v>105127.0718604963</v>
+        <v>105338.4569268588</v>
       </c>
       <c r="M6" t="n">
-        <v>105127.0718604963</v>
+        <v>105338.4569268588</v>
       </c>
       <c r="N6" t="n">
-        <v>105127.0718604963</v>
+        <v>105338.4569268588</v>
       </c>
       <c r="O6" t="n">
-        <v>105127.0718604963</v>
+        <v>105338.4569268588</v>
       </c>
       <c r="P6" t="n">
-        <v>105127.0718604963</v>
+        <v>105338.4569268588</v>
       </c>
     </row>
   </sheetData>
@@ -26675,49 +26675,49 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>11.80207166992776</v>
       </c>
       <c r="C3" t="n">
-        <v>232</v>
+        <v>234.7800381259942</v>
       </c>
       <c r="D3" t="n">
-        <v>260</v>
+        <v>260.7963925174648</v>
       </c>
       <c r="E3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="F3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="G3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="H3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="I3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="J3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="K3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="L3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="M3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="N3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="O3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="P3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
     </row>
     <row r="4">
@@ -26892,22 +26892,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>11.80207166992776</v>
       </c>
       <c r="C3" t="n">
-        <v>218</v>
+        <v>222.9779664560664</v>
       </c>
       <c r="D3" t="n">
-        <v>28</v>
+        <v>26.01635439147063</v>
       </c>
       <c r="E3" t="n">
-        <v>60</v>
+        <v>59.02482598057778</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -26953,34 +26953,34 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -27301,31 +27301,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>382.7338416634807</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C2" t="n">
-        <v>365.2728917710077</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D2" t="n">
-        <v>354.6830416206831</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E2" t="n">
-        <v>381.9303700722619</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F2" t="n">
-        <v>400.0000000000002</v>
+        <v>400</v>
       </c>
       <c r="G2" t="n">
-        <v>400.0000000000002</v>
+        <v>400</v>
       </c>
       <c r="H2" t="n">
-        <v>338.8984101559682</v>
+        <v>338.9889007429445</v>
       </c>
       <c r="I2" t="n">
-        <v>208.3061006256823</v>
+        <v>208.6467463822455</v>
       </c>
       <c r="J2" t="n">
-        <v>7.17247528426077</v>
+        <v>7.922410639454604</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -27346,31 +27346,31 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.912940420574955</v>
+        <v>4.867117437475816</v>
       </c>
       <c r="R2" t="n">
-        <v>146.3337310064763</v>
+        <v>146.8887686565824</v>
       </c>
       <c r="S2" t="n">
-        <v>207.7375570234313</v>
+        <v>207.9389049302515</v>
       </c>
       <c r="T2" t="n">
-        <v>222.8494777048349</v>
+        <v>222.8881568254978</v>
       </c>
       <c r="U2" t="n">
-        <v>251.3411503952737</v>
+        <v>251.3418572666964</v>
       </c>
       <c r="V2" t="n">
-        <v>327.752258470135</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W2" t="n">
-        <v>349.2409687174131</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X2" t="n">
-        <v>369.7311006784691</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y2" t="n">
-        <v>386.2379386560537</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="3">
@@ -27380,28 +27380,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>166.5331836498674</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C3" t="n">
-        <v>172.7084989883158</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D3" t="n">
         <v>147.4450655646388</v>
       </c>
       <c r="E3" t="n">
-        <v>157.645080455401</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F3" t="n">
         <v>145.0692123933839</v>
       </c>
       <c r="G3" t="n">
-        <v>137.3134039556635</v>
+        <v>137.3181315750904</v>
       </c>
       <c r="H3" t="n">
-        <v>111.9446140478172</v>
+        <v>111.9902728985985</v>
       </c>
       <c r="I3" t="n">
-        <v>88.35984039858489</v>
+        <v>88.52261150604778</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27428,28 +27428,28 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>98.28817377528465</v>
+        <v>98.58170088321391</v>
       </c>
       <c r="S3" t="n">
-        <v>171.1238314811963</v>
+        <v>171.2116449385346</v>
       </c>
       <c r="T3" t="n">
-        <v>200.043351336331</v>
+        <v>200.0624069602493</v>
       </c>
       <c r="U3" t="n">
-        <v>225.9394009488993</v>
+        <v>225.9397119764932</v>
       </c>
       <c r="V3" t="n">
-        <v>232.8005871494254</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W3" t="n">
-        <v>251.6949831609197</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X3" t="n">
-        <v>205.7729852034776</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y3" t="n">
-        <v>205.6826957773045</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="4">
@@ -27459,10 +27459,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>179.8319801819374</v>
+        <v>179.8319801819373</v>
       </c>
       <c r="C4" t="n">
-        <v>167.2468210986279</v>
+        <v>167.2468210986278</v>
       </c>
       <c r="D4" t="n">
         <v>148.6154730182124</v>
@@ -27471,22 +27471,22 @@
         <v>146.4339626465692</v>
       </c>
       <c r="F4" t="n">
-        <v>145.4210480229313</v>
+        <v>145.4210480229312</v>
       </c>
       <c r="G4" t="n">
-        <v>167.9657334568194</v>
+        <v>167.9696969341359</v>
       </c>
       <c r="H4" t="n">
-        <v>162.0027134910461</v>
+        <v>162.0379524075512</v>
       </c>
       <c r="I4" t="n">
-        <v>154.6912618125042</v>
+        <v>154.8104543848956</v>
       </c>
       <c r="J4" t="n">
-        <v>91.57429487077114</v>
+        <v>91.85451271704936</v>
       </c>
       <c r="K4" t="n">
-        <v>19.33637707178449</v>
+        <v>19.79686107274061</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -27501,34 +27501,34 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.1474282515537451</v>
       </c>
       <c r="Q4" t="n">
-        <v>84.04804325169438</v>
+        <v>84.37993042953529</v>
       </c>
       <c r="R4" t="n">
-        <v>176.1582438361859</v>
+        <v>176.3364561889816</v>
       </c>
       <c r="S4" t="n">
-        <v>223.5766308238575</v>
+        <v>223.6457034240009</v>
       </c>
       <c r="T4" t="n">
-        <v>227.8377205758225</v>
+        <v>227.8546554334476</v>
       </c>
       <c r="U4" t="n">
-        <v>286.3176523073105</v>
+        <v>286.3178684969824</v>
       </c>
       <c r="V4" t="n">
-        <v>252.1376433238281</v>
+        <v>252.137643323828</v>
       </c>
       <c r="W4" t="n">
-        <v>286.5229983365911</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X4" t="n">
-        <v>225.7096553890373</v>
+        <v>225.7096553890372</v>
       </c>
       <c r="Y4" t="n">
-        <v>218.5846533520949</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="5">
@@ -27538,28 +27538,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>382.7338416634808</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C5" t="n">
-        <v>365.272891771008</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D5" t="n">
-        <v>354.6830416206832</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E5" t="n">
-        <v>381.930370072262</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F5" t="n">
-        <v>400.0000000000001</v>
+        <v>400</v>
       </c>
       <c r="G5" t="n">
-        <v>400.0000000000001</v>
+        <v>400</v>
       </c>
       <c r="H5" t="n">
-        <v>329.9231639248124</v>
+        <v>329.8087073802583</v>
       </c>
       <c r="I5" t="n">
-        <v>174.5193870578431</v>
+        <v>174.0885230584365</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27586,28 +27586,28 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>91.28270588084817</v>
+        <v>90.58066941881005</v>
       </c>
       <c r="S5" t="n">
-        <v>187.7670042596122</v>
+        <v>187.5123304152058</v>
       </c>
       <c r="T5" t="n">
-        <v>219.0131158957896</v>
+        <v>218.9641928127885</v>
       </c>
       <c r="U5" t="n">
-        <v>251.2710398425099</v>
+        <v>251.2701457598965</v>
       </c>
       <c r="V5" t="n">
-        <v>327.7522584701351</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W5" t="n">
-        <v>349.2409687174132</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X5" t="n">
-        <v>369.7311006784693</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y5" t="n">
-        <v>386.2379386560539</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="6">
@@ -27617,28 +27617,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>166.5331836498674</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C6" t="n">
-        <v>172.7084989883158</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D6" t="n">
         <v>147.4450655646388</v>
       </c>
       <c r="E6" t="n">
-        <v>157.645080455401</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F6" t="n">
         <v>145.0692123933839</v>
       </c>
       <c r="G6" t="n">
-        <v>136.8444982952861</v>
+        <v>136.8385185906377</v>
       </c>
       <c r="H6" t="n">
-        <v>107.4159725383833</v>
+        <v>107.3582211803319</v>
       </c>
       <c r="I6" t="n">
-        <v>72.21550077594338</v>
+        <v>72.00962059397116</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27665,28 +27665,28 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>69.1748907564167</v>
+        <v>68.80362453272261</v>
       </c>
       <c r="S6" t="n">
-        <v>162.4141145000642</v>
+        <v>162.3030441088983</v>
       </c>
       <c r="T6" t="n">
-        <v>198.1533324684065</v>
+        <v>198.1292300623896</v>
       </c>
       <c r="U6" t="n">
-        <v>225.9085518922956</v>
+        <v>225.908158490674</v>
       </c>
       <c r="V6" t="n">
-        <v>232.8005871494254</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W6" t="n">
-        <v>251.6949831609197</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X6" t="n">
-        <v>205.7729852034776</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y6" t="n">
-        <v>205.6826957773045</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="7">
@@ -27696,31 +27696,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>179.8319801819374</v>
+        <v>179.8319801819373</v>
       </c>
       <c r="C7" t="n">
-        <v>167.2468210986279</v>
+        <v>167.2468210986278</v>
       </c>
       <c r="D7" t="n">
-        <v>148.6154730182112</v>
+        <v>148.6154730182124</v>
       </c>
       <c r="E7" t="n">
         <v>146.4339626465692</v>
       </c>
       <c r="F7" t="n">
-        <v>145.4210480229313</v>
+        <v>145.4210480229312</v>
       </c>
       <c r="G7" t="n">
-        <v>167.5726187027211</v>
+        <v>167.5676055192152</v>
       </c>
       <c r="H7" t="n">
-        <v>158.5075659500625</v>
+        <v>158.4629941912556</v>
       </c>
       <c r="I7" t="n">
-        <v>142.8692290256189</v>
+        <v>142.7184689252781</v>
       </c>
       <c r="J7" t="n">
-        <v>63.78108175601704</v>
+        <v>63.42664968215054</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -27741,31 +27741,31 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>51.13004325169438</v>
+        <v>50.71025749466926</v>
       </c>
       <c r="R7" t="n">
-        <v>158.4823749837269</v>
+        <v>158.2569640235438</v>
       </c>
       <c r="S7" t="n">
-        <v>216.7257127910706</v>
+        <v>216.6383466748816</v>
       </c>
       <c r="T7" t="n">
-        <v>226.1580484446749</v>
+        <v>226.1366284787861</v>
       </c>
       <c r="U7" t="n">
-        <v>286.2962096843597</v>
+        <v>286.2959362379867</v>
       </c>
       <c r="V7" t="n">
-        <v>252.1376433238281</v>
+        <v>252.137643323828</v>
       </c>
       <c r="W7" t="n">
-        <v>286.5229983365911</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X7" t="n">
-        <v>225.7096553890373</v>
+        <v>225.7096553890372</v>
       </c>
       <c r="Y7" t="n">
-        <v>218.5846533520949</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="8">
@@ -27775,28 +27775,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>382.7338416634808</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C8" t="n">
-        <v>365.2728917710078</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D8" t="n">
-        <v>354.6830416206832</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E8" t="n">
-        <v>381.930370072262</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F8" t="n">
-        <v>400.0000000000001</v>
+        <v>400</v>
       </c>
       <c r="G8" t="n">
-        <v>400.0000000000001</v>
+        <v>400</v>
       </c>
       <c r="H8" t="n">
-        <v>328.7703800052144</v>
+        <v>328.737591844935</v>
       </c>
       <c r="I8" t="n">
-        <v>170.1798091683958</v>
+        <v>170.0563803341062</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27823,28 +27823,28 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>84.21193201150143</v>
+        <v>84.01082088999308</v>
       </c>
       <c r="S8" t="n">
-        <v>185.201979133984</v>
+        <v>185.1290231762283</v>
       </c>
       <c r="T8" t="n">
-        <v>218.5203721771967</v>
+        <v>218.5063572696783</v>
       </c>
       <c r="U8" t="n">
-        <v>251.2620348173842</v>
+        <v>251.2617786911475</v>
       </c>
       <c r="V8" t="n">
-        <v>327.752258470135</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W8" t="n">
-        <v>349.2409687174132</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X8" t="n">
-        <v>369.7311006784693</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y8" t="n">
-        <v>386.2379386560539</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="9">
@@ -27854,28 +27854,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>166.5331836498674</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C9" t="n">
-        <v>172.7084989883158</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D9" t="n">
         <v>147.4450655646388</v>
       </c>
       <c r="E9" t="n">
-        <v>157.645080455401</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F9" t="n">
         <v>145.0692123933839</v>
       </c>
       <c r="G9" t="n">
-        <v>136.7842718801918</v>
+        <v>136.7825588849655</v>
       </c>
       <c r="H9" t="n">
-        <v>106.8343121610248</v>
+        <v>106.817768233445</v>
       </c>
       <c r="I9" t="n">
-        <v>70.141915870283</v>
+        <v>70.08293774516886</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -27902,28 +27902,28 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>65.43557000169972</v>
+        <v>65.32921403493339</v>
       </c>
       <c r="S9" t="n">
-        <v>161.2954352547812</v>
+        <v>161.2636171197674</v>
       </c>
       <c r="T9" t="n">
-        <v>197.9105777514254</v>
+        <v>197.9036731785617</v>
       </c>
       <c r="U9" t="n">
-        <v>225.9045896281446</v>
+        <v>225.9044769310903</v>
       </c>
       <c r="V9" t="n">
-        <v>232.8005871494254</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W9" t="n">
-        <v>251.6949831609197</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X9" t="n">
-        <v>205.7729852034776</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y9" t="n">
-        <v>205.6826957773045</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="10">
@@ -27933,10 +27933,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>179.8319801819345</v>
+        <v>179.8319801819373</v>
       </c>
       <c r="C10" t="n">
-        <v>167.2468210986279</v>
+        <v>167.2468210986278</v>
       </c>
       <c r="D10" t="n">
         <v>148.6154730182124</v>
@@ -27945,19 +27945,19 @@
         <v>146.4339626465692</v>
       </c>
       <c r="F10" t="n">
-        <v>145.4210480229313</v>
+        <v>145.4210480229312</v>
       </c>
       <c r="G10" t="n">
-        <v>167.5221268994424</v>
+        <v>167.5206907817879</v>
       </c>
       <c r="H10" t="n">
-        <v>158.0586479172756</v>
+        <v>158.0458795257661</v>
       </c>
       <c r="I10" t="n">
-        <v>141.3508027961107</v>
+        <v>141.3076148215571</v>
       </c>
       <c r="J10" t="n">
-        <v>60.21131126421376</v>
+        <v>60.10977774604451</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -27978,31 +27978,31 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>46.90204325169438</v>
+        <v>46.78178798155719</v>
       </c>
       <c r="R10" t="n">
-        <v>156.2120799017596</v>
+        <v>156.1475068297698</v>
       </c>
       <c r="S10" t="n">
-        <v>215.8457783648411</v>
+        <v>215.8207507508087</v>
       </c>
       <c r="T10" t="n">
-        <v>225.9423107397569</v>
+        <v>225.9361746006879</v>
       </c>
       <c r="U10" t="n">
-        <v>286.2934555859991</v>
+        <v>286.2933772523089</v>
       </c>
       <c r="V10" t="n">
-        <v>252.1376433238281</v>
+        <v>252.137643323828</v>
       </c>
       <c r="W10" t="n">
-        <v>286.5229983365911</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X10" t="n">
-        <v>225.7096553890373</v>
+        <v>225.7096553890372</v>
       </c>
       <c r="Y10" t="n">
-        <v>218.5846533520949</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="11">
@@ -30959,49 +30959,49 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05628140703517586</v>
+        <v>0.04744551425096582</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5763919597989949</v>
+        <v>0.4859013728227038</v>
       </c>
       <c r="I2" t="n">
-        <v>2.169788944723618</v>
+        <v>1.829143188160361</v>
       </c>
       <c r="J2" t="n">
-        <v>4.77681407035176</v>
+        <v>4.026878715157913</v>
       </c>
       <c r="K2" t="n">
-        <v>7.159206030150757</v>
+        <v>6.035247333401298</v>
       </c>
       <c r="L2" t="n">
-        <v>8.881628140703519</v>
+        <v>7.487257990159295</v>
       </c>
       <c r="M2" t="n">
-        <v>9.882522613065326</v>
+        <v>8.331017154219907</v>
       </c>
       <c r="N2" t="n">
-        <v>10.04243216080402</v>
+        <v>8.465821721585465</v>
       </c>
       <c r="O2" t="n">
-        <v>9.48278391959799</v>
+        <v>7.994035389252423</v>
       </c>
       <c r="P2" t="n">
-        <v>8.093336683417087</v>
+        <v>6.822724256181703</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.077758793969849</v>
+        <v>5.123581777068988</v>
       </c>
       <c r="R2" t="n">
-        <v>3.535386934673367</v>
+        <v>2.980349284567234</v>
       </c>
       <c r="S2" t="n">
-        <v>1.282512562814071</v>
+        <v>1.081164655993885</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2463718592964824</v>
+        <v>0.207692738633603</v>
       </c>
       <c r="U2" t="n">
-        <v>0.004502512562814065</v>
+        <v>0.003795641140077265</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -31038,49 +31038,49 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03011320754716981</v>
+        <v>0.02538558812022196</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2908301886792454</v>
+        <v>0.2451713378979332</v>
       </c>
       <c r="I3" t="n">
-        <v>1.036792452830189</v>
+        <v>0.8740213453672915</v>
       </c>
       <c r="J3" t="n">
-        <v>2.845037735849057</v>
+        <v>2.398381375867112</v>
       </c>
       <c r="K3" t="n">
-        <v>4.862622641509436</v>
+        <v>4.099215779921983</v>
       </c>
       <c r="L3" t="n">
-        <v>6.538396226415097</v>
+        <v>5.511901490752582</v>
       </c>
       <c r="M3" t="n">
-        <v>7.630000000000003</v>
+        <v>6.432129060110626</v>
       </c>
       <c r="N3" t="n">
-        <v>7.831943396226419</v>
+        <v>6.602368376934397</v>
       </c>
       <c r="O3" t="n">
-        <v>7.16469811320755</v>
+        <v>6.039877187533688</v>
       </c>
       <c r="P3" t="n">
-        <v>5.750301886792455</v>
+        <v>4.847533927974667</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.843924528301889</v>
+        <v>3.24044805548658</v>
       </c>
       <c r="R3" t="n">
-        <v>1.869660377358491</v>
+        <v>1.57613326942922</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5593396226415092</v>
+        <v>0.4715261653032454</v>
       </c>
       <c r="T3" t="n">
-        <v>0.121377358490566</v>
+        <v>0.1023217345722982</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001981132075471699</v>
+        <v>0.001670104481593551</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -31117,49 +31117,49 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02524590163934426</v>
+        <v>0.02128242432282054</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2244590163934428</v>
+        <v>0.18922009988835</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7592131147540987</v>
+        <v>0.6400205423626397</v>
       </c>
       <c r="J4" t="n">
-        <v>1.78488524590164</v>
+        <v>1.504667399623412</v>
       </c>
       <c r="K4" t="n">
-        <v>2.93311475409836</v>
+        <v>2.472630753142241</v>
       </c>
       <c r="L4" t="n">
-        <v>3.75337704918033</v>
+        <v>3.164116067049156</v>
       </c>
       <c r="M4" t="n">
-        <v>3.957409836065574</v>
+        <v>3.336116750894496</v>
       </c>
       <c r="N4" t="n">
-        <v>3.86331147540984</v>
+        <v>3.256791351145804</v>
       </c>
       <c r="O4" t="n">
-        <v>3.568393442622953</v>
+        <v>3.008173939738308</v>
       </c>
       <c r="P4" t="n">
-        <v>3.053377049180326</v>
+        <v>2.574012483552767</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.114</v>
+        <v>1.782112822159091</v>
       </c>
       <c r="R4" t="n">
-        <v>1.135147540983606</v>
+        <v>0.9569351881879125</v>
       </c>
       <c r="S4" t="n">
-        <v>0.439967213114754</v>
+        <v>0.370894612971336</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1078688524590164</v>
+        <v>0.09093399483386956</v>
       </c>
       <c r="U4" t="n">
-        <v>0.00137704918032787</v>
+        <v>0.001160859508517485</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -31196,49 +31196,49 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.932663316582914</v>
+        <v>0.9438393492502272</v>
       </c>
       <c r="H5" t="n">
-        <v>9.551638190954771</v>
+        <v>9.666094735508892</v>
       </c>
       <c r="I5" t="n">
-        <v>35.95650251256282</v>
+        <v>36.38736651196942</v>
       </c>
       <c r="J5" t="n">
-        <v>79.15863316582916</v>
+        <v>80.10718496842655</v>
       </c>
       <c r="K5" t="n">
-        <v>118.638271356784</v>
+        <v>120.0599046221887</v>
       </c>
       <c r="L5" t="n">
-        <v>147.1812663316583</v>
+        <v>148.9449281068054</v>
       </c>
       <c r="M5" t="n">
-        <v>163.7675175879397</v>
+        <v>165.7299311340341</v>
       </c>
       <c r="N5" t="n">
-        <v>166.4174472361809</v>
+        <v>168.4116146850913</v>
       </c>
       <c r="O5" t="n">
-        <v>157.1432763819096</v>
+        <v>159.0263121559843</v>
       </c>
       <c r="P5" t="n">
-        <v>134.1181507537689</v>
+        <v>135.7252782213693</v>
       </c>
       <c r="Q5" t="n">
-        <v>100.7171457286432</v>
+        <v>101.9240315263455</v>
       </c>
       <c r="R5" t="n">
-        <v>58.58641206030151</v>
+        <v>59.28844852233964</v>
       </c>
       <c r="S5" t="n">
-        <v>21.25306532663317</v>
+        <v>21.50773917103957</v>
       </c>
       <c r="T5" t="n">
-        <v>4.082733668341708</v>
+        <v>4.131656751342871</v>
       </c>
       <c r="U5" t="n">
-        <v>0.07461306532663309</v>
+        <v>0.07550714794001816</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -31275,49 +31275,49 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4990188679245283</v>
+        <v>0.5049985725728932</v>
       </c>
       <c r="H6" t="n">
-        <v>4.819471698113209</v>
+        <v>4.877223056164522</v>
       </c>
       <c r="I6" t="n">
-        <v>17.1811320754717</v>
+        <v>17.38701225744391</v>
       </c>
       <c r="J6" t="n">
-        <v>47.14633962264153</v>
+        <v>47.71129057803813</v>
       </c>
       <c r="K6" t="n">
-        <v>80.58060377358493</v>
+        <v>81.54619494042197</v>
       </c>
       <c r="L6" t="n">
-        <v>108.3505660377359</v>
+        <v>109.6489225228995</v>
       </c>
       <c r="M6" t="n">
-        <v>126.44</v>
+        <v>127.9551207786668</v>
       </c>
       <c r="N6" t="n">
-        <v>129.7864905660377</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O6" t="n">
-        <v>118.729283018868</v>
+        <v>120.1520068700076</v>
       </c>
       <c r="P6" t="n">
-        <v>95.29071698113209</v>
+        <v>96.43257830122204</v>
       </c>
       <c r="Q6" t="n">
-        <v>63.69932075471699</v>
+        <v>64.4626248077258</v>
       </c>
       <c r="R6" t="n">
-        <v>30.98294339622643</v>
+        <v>31.35420961992052</v>
       </c>
       <c r="S6" t="n">
-        <v>9.26905660377358</v>
+        <v>9.380126994939479</v>
       </c>
       <c r="T6" t="n">
-        <v>2.011396226415094</v>
+        <v>2.035498632431968</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0328301886792453</v>
+        <v>0.03322359030084825</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -31354,49 +31354,49 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4183606557377049</v>
+        <v>0.423373839243596</v>
       </c>
       <c r="H7" t="n">
-        <v>3.719606557377052</v>
+        <v>3.764178316183975</v>
       </c>
       <c r="I7" t="n">
-        <v>12.58124590163935</v>
+        <v>12.73200600198015</v>
       </c>
       <c r="J7" t="n">
-        <v>29.57809836065574</v>
+        <v>29.93253043452224</v>
       </c>
       <c r="K7" t="n">
-        <v>48.60590163934426</v>
+        <v>49.18834241393778</v>
       </c>
       <c r="L7" t="n">
-        <v>62.19881967213116</v>
+        <v>62.94414333627064</v>
       </c>
       <c r="M7" t="n">
-        <v>65.5799344262295</v>
+        <v>66.36577372797568</v>
       </c>
       <c r="N7" t="n">
-        <v>64.02059016393447</v>
+        <v>64.78774396352233</v>
       </c>
       <c r="O7" t="n">
-        <v>59.13337704918035</v>
+        <v>59.84196775054031</v>
       </c>
       <c r="P7" t="n">
-        <v>50.59881967213114</v>
+        <v>51.20514142997091</v>
       </c>
       <c r="Q7" t="n">
-        <v>35.032</v>
+        <v>35.45178575702513</v>
       </c>
       <c r="R7" t="n">
-        <v>18.81101639344262</v>
+        <v>19.03642735362569</v>
       </c>
       <c r="S7" t="n">
-        <v>7.290885245901637</v>
+        <v>7.378251362090667</v>
       </c>
       <c r="T7" t="n">
-        <v>1.787540983606557</v>
+        <v>1.808960949495364</v>
       </c>
       <c r="U7" t="n">
-        <v>0.02281967213114757</v>
+        <v>0.02309311850419617</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -31433,49 +31433,49 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1.045226130653266</v>
+        <v>1.048427708612923</v>
       </c>
       <c r="H8" t="n">
-        <v>10.70442211055276</v>
+        <v>10.7372102708321</v>
       </c>
       <c r="I8" t="n">
-        <v>40.29608040201006</v>
+        <v>40.41950923629976</v>
       </c>
       <c r="J8" t="n">
-        <v>88.71226130653267</v>
+        <v>88.98399123388617</v>
       </c>
       <c r="K8" t="n">
-        <v>132.9566834170854</v>
+        <v>133.3639361394712</v>
       </c>
       <c r="L8" t="n">
-        <v>164.9445226130653</v>
+        <v>165.449755626934</v>
       </c>
       <c r="M8" t="n">
-        <v>183.5325628140703</v>
+        <v>184.0947318899791</v>
       </c>
       <c r="N8" t="n">
-        <v>186.5023115577889</v>
+        <v>187.0735771170756</v>
       </c>
       <c r="O8" t="n">
-        <v>176.1088442211055</v>
+        <v>176.6482740895558</v>
       </c>
       <c r="P8" t="n">
-        <v>150.304824120603</v>
+        <v>150.7652150331742</v>
       </c>
       <c r="Q8" t="n">
-        <v>112.8726633165829</v>
+        <v>113.2183977184739</v>
       </c>
       <c r="R8" t="n">
-        <v>65.65718592964825</v>
+        <v>65.8582970511566</v>
       </c>
       <c r="S8" t="n">
-        <v>23.81809045226132</v>
+        <v>23.89104641001701</v>
       </c>
       <c r="T8" t="n">
-        <v>4.575477386934673</v>
+        <v>4.589492294453073</v>
       </c>
       <c r="U8" t="n">
-        <v>0.08361809045226123</v>
+        <v>0.08387421668903385</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -31512,49 +31512,49 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.559245283018868</v>
+        <v>0.560958278245113</v>
       </c>
       <c r="H9" t="n">
-        <v>5.4011320754717</v>
+        <v>5.417676003051488</v>
       </c>
       <c r="I9" t="n">
-        <v>19.25471698113208</v>
+        <v>19.31369510624622</v>
       </c>
       <c r="J9" t="n">
-        <v>52.83641509433964</v>
+        <v>52.99825557753501</v>
       </c>
       <c r="K9" t="n">
-        <v>90.30584905660378</v>
+        <v>90.58246021995758</v>
       </c>
       <c r="L9" t="n">
-        <v>121.427358490566</v>
+        <v>121.799296335633</v>
       </c>
       <c r="M9" t="n">
-        <v>141.7</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N9" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O9" t="n">
-        <v>133.058679245283</v>
+        <v>133.4662443858011</v>
       </c>
       <c r="P9" t="n">
-        <v>106.791320754717</v>
+        <v>107.1184277115602</v>
       </c>
       <c r="Q9" t="n">
-        <v>71.38716981132077</v>
+        <v>71.60583214932356</v>
       </c>
       <c r="R9" t="n">
-        <v>34.72226415094342</v>
+        <v>34.82862011770975</v>
       </c>
       <c r="S9" t="n">
-        <v>10.3877358490566</v>
+        <v>10.41955398407041</v>
       </c>
       <c r="T9" t="n">
-        <v>2.254150943396226</v>
+        <v>2.261055516259907</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03679245283018871</v>
+        <v>0.03690514988454693</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -31591,49 +31591,49 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4688524590163934</v>
+        <v>0.4702885766708382</v>
       </c>
       <c r="H10" t="n">
-        <v>4.168524590163938</v>
+        <v>4.181292981673455</v>
       </c>
       <c r="I10" t="n">
-        <v>14.09967213114755</v>
+        <v>14.14286010570121</v>
       </c>
       <c r="J10" t="n">
-        <v>33.14786885245902</v>
+        <v>33.24940237062826</v>
       </c>
       <c r="K10" t="n">
-        <v>54.47213114754096</v>
+        <v>54.63898190775737</v>
       </c>
       <c r="L10" t="n">
-        <v>69.70557377049181</v>
+        <v>69.91908529886263</v>
       </c>
       <c r="M10" t="n">
-        <v>73.49475409836064</v>
+        <v>73.71987206850237</v>
       </c>
       <c r="N10" t="n">
-        <v>71.74721311475415</v>
+        <v>71.96697828272931</v>
       </c>
       <c r="O10" t="n">
-        <v>66.27016393442625</v>
+        <v>66.47315263707451</v>
       </c>
       <c r="P10" t="n">
-        <v>56.70557377049178</v>
+        <v>56.87926567298936</v>
       </c>
       <c r="Q10" t="n">
-        <v>39.26000000000001</v>
+        <v>39.38025527013719</v>
       </c>
       <c r="R10" t="n">
-        <v>21.08131147540983</v>
+        <v>21.14588454739968</v>
       </c>
       <c r="S10" t="n">
-        <v>8.170819672131145</v>
+        <v>8.195847286163604</v>
       </c>
       <c r="T10" t="n">
-        <v>2.00327868852459</v>
+        <v>2.009414827593581</v>
       </c>
       <c r="U10" t="n">
-        <v>0.02557377049180331</v>
+        <v>0.02565210418204575</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -31670,49 +31670,49 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.286432160804019</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H11" t="n">
-        <v>13.17467336683417</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I11" t="n">
-        <v>49.595175879397</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J11" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K11" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L11" t="n">
-        <v>203.0086432160804</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M11" t="n">
-        <v>225.8862311557789</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N11" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O11" t="n">
-        <v>216.7493467336683</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P11" t="n">
-        <v>184.9905527638191</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q11" t="n">
-        <v>138.9202010050251</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R11" t="n">
-        <v>80.80884422110556</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S11" t="n">
-        <v>29.31457286432163</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T11" t="n">
-        <v>5.631356783919598</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -31749,19 +31749,19 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6883018867924529</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H12" t="n">
-        <v>6.647547169811324</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I12" t="n">
-        <v>23.69811320754718</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J12" t="n">
-        <v>65.02943396226418</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K12" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L12" t="n">
         <v>138.5543797798742</v>
@@ -31776,22 +31776,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P12" t="n">
-        <v>131.4354716981132</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q12" t="n">
-        <v>87.86113207547173</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R12" t="n">
-        <v>42.73509433962267</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S12" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T12" t="n">
-        <v>2.774339622641509</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U12" t="n">
-        <v>0.04528301886792455</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -31828,49 +31828,49 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5770491803278688</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H13" t="n">
-        <v>5.130491803278693</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I13" t="n">
-        <v>17.35344262295083</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J13" t="n">
-        <v>40.79737704918034</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K13" t="n">
-        <v>67.04262295081968</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L13" t="n">
-        <v>85.79147540983608</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M13" t="n">
-        <v>90.4550819672131</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N13" t="n">
-        <v>88.30426229508203</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O13" t="n">
-        <v>81.56327868852462</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P13" t="n">
-        <v>69.79147540983605</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q13" t="n">
-        <v>48.32000000000001</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R13" t="n">
-        <v>25.94622950819672</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S13" t="n">
-        <v>10.05639344262295</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T13" t="n">
-        <v>2.465573770491803</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U13" t="n">
-        <v>0.03147540983606561</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -31907,49 +31907,49 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.286432160804019</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H14" t="n">
-        <v>13.17467336683416</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I14" t="n">
-        <v>49.59517587939698</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J14" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K14" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L14" t="n">
-        <v>203.0086432160804</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M14" t="n">
-        <v>225.8862311557789</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N14" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O14" t="n">
-        <v>216.7493467336683</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P14" t="n">
-        <v>184.9905527638191</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q14" t="n">
-        <v>138.9202010050251</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R14" t="n">
-        <v>80.80884422110553</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S14" t="n">
-        <v>29.31457286432162</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T14" t="n">
-        <v>5.631356783919594</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -31986,19 +31986,19 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6883018867924529</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H15" t="n">
-        <v>6.647547169811319</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I15" t="n">
-        <v>23.69811320754717</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J15" t="n">
-        <v>65.02943396226415</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K15" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L15" t="n">
         <v>138.5543797798742</v>
@@ -32013,22 +32013,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P15" t="n">
-        <v>131.4354716981132</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q15" t="n">
-        <v>87.86113207547172</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R15" t="n">
-        <v>42.73509433962265</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S15" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T15" t="n">
-        <v>2.774339622641507</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U15" t="n">
-        <v>0.04528301886792455</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -32065,49 +32065,49 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5770491803278688</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H16" t="n">
-        <v>5.130491803278689</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I16" t="n">
-        <v>17.35344262295082</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J16" t="n">
-        <v>40.79737704918032</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K16" t="n">
-        <v>67.04262295081968</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L16" t="n">
-        <v>85.79147540983608</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M16" t="n">
-        <v>90.4550819672131</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N16" t="n">
-        <v>88.30426229508203</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O16" t="n">
-        <v>81.56327868852462</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P16" t="n">
-        <v>69.79147540983605</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q16" t="n">
-        <v>48.31999999999999</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R16" t="n">
-        <v>25.94622950819671</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S16" t="n">
-        <v>10.05639344262294</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T16" t="n">
-        <v>2.465573770491801</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U16" t="n">
-        <v>0.03147540983606561</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -32144,49 +32144,49 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.286432160804019</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H17" t="n">
-        <v>13.17467336683416</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I17" t="n">
-        <v>49.59517587939698</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J17" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K17" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L17" t="n">
-        <v>203.0086432160804</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M17" t="n">
-        <v>225.8862311557789</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N17" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O17" t="n">
-        <v>216.7493467336683</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P17" t="n">
-        <v>184.9905527638191</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q17" t="n">
-        <v>138.9202010050251</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R17" t="n">
-        <v>80.80884422110553</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S17" t="n">
-        <v>29.31457286432162</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T17" t="n">
-        <v>5.631356783919594</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -32223,19 +32223,19 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6883018867924529</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H18" t="n">
-        <v>6.647547169811319</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I18" t="n">
-        <v>23.69811320754717</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J18" t="n">
-        <v>65.02943396226415</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K18" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L18" t="n">
         <v>138.5543797798742</v>
@@ -32250,22 +32250,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P18" t="n">
-        <v>131.4354716981132</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q18" t="n">
-        <v>87.86113207547172</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R18" t="n">
-        <v>42.73509433962265</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S18" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T18" t="n">
-        <v>2.774339622641508</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U18" t="n">
-        <v>0.04528301886792455</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -32302,49 +32302,49 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5770491803278688</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H19" t="n">
-        <v>5.130491803278689</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I19" t="n">
-        <v>17.35344262295082</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J19" t="n">
-        <v>40.79737704918032</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K19" t="n">
-        <v>67.04262295081968</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L19" t="n">
-        <v>85.79147540983608</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M19" t="n">
-        <v>90.4550819672131</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N19" t="n">
-        <v>88.30426229508203</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O19" t="n">
-        <v>81.56327868852462</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P19" t="n">
-        <v>69.79147540983605</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q19" t="n">
-        <v>48.31999999999999</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R19" t="n">
-        <v>25.94622950819671</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S19" t="n">
-        <v>10.05639344262294</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T19" t="n">
-        <v>2.465573770491802</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U19" t="n">
-        <v>0.03147540983606561</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -32381,49 +32381,49 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>1.286432160804019</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H20" t="n">
-        <v>13.17467336683416</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I20" t="n">
-        <v>49.59517587939698</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J20" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K20" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L20" t="n">
-        <v>203.0086432160804</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M20" t="n">
-        <v>225.8862311557789</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N20" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O20" t="n">
-        <v>216.7493467336683</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P20" t="n">
-        <v>184.9905527638191</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q20" t="n">
-        <v>138.9202010050251</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R20" t="n">
-        <v>80.80884422110553</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S20" t="n">
-        <v>29.31457286432162</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T20" t="n">
-        <v>5.631356783919594</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -32460,19 +32460,19 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6883018867924529</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H21" t="n">
-        <v>6.647547169811319</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I21" t="n">
-        <v>23.69811320754717</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J21" t="n">
-        <v>65.02943396226418</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K21" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L21" t="n">
         <v>138.5543797798742</v>
@@ -32487,22 +32487,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P21" t="n">
-        <v>131.4354716981132</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q21" t="n">
-        <v>87.86113207547172</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R21" t="n">
-        <v>42.73509433962265</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S21" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T21" t="n">
-        <v>2.774339622641508</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U21" t="n">
-        <v>0.04528301886792455</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -32539,49 +32539,49 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5770491803278688</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H22" t="n">
-        <v>5.130491803278689</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I22" t="n">
-        <v>17.35344262295082</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J22" t="n">
-        <v>40.79737704918032</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K22" t="n">
-        <v>67.04262295081968</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L22" t="n">
-        <v>85.79147540983608</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M22" t="n">
-        <v>90.4550819672131</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N22" t="n">
-        <v>88.30426229508203</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O22" t="n">
-        <v>81.56327868852462</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P22" t="n">
-        <v>69.79147540983605</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q22" t="n">
-        <v>48.31999999999999</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R22" t="n">
-        <v>25.94622950819671</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S22" t="n">
-        <v>10.05639344262294</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T22" t="n">
-        <v>2.465573770491802</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U22" t="n">
-        <v>0.03147540983606561</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -32618,49 +32618,49 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>1.286432160804019</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H23" t="n">
-        <v>13.17467336683417</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I23" t="n">
-        <v>49.595175879397</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J23" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K23" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L23" t="n">
-        <v>203.0086432160805</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M23" t="n">
-        <v>225.8862311557789</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N23" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O23" t="n">
-        <v>216.7493467336684</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P23" t="n">
-        <v>184.9905527638191</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q23" t="n">
-        <v>138.9202010050251</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R23" t="n">
-        <v>80.80884422110556</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S23" t="n">
-        <v>29.31457286432162</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T23" t="n">
-        <v>5.631356783919597</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -32697,19 +32697,19 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.688301886792453</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H24" t="n">
-        <v>6.647547169811324</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I24" t="n">
-        <v>23.69811320754718</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J24" t="n">
-        <v>65.02943396226418</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K24" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L24" t="n">
         <v>138.5543797798742</v>
@@ -32724,22 +32724,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P24" t="n">
-        <v>131.4354716981132</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q24" t="n">
-        <v>87.86113207547173</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R24" t="n">
-        <v>42.73509433962267</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S24" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T24" t="n">
-        <v>2.774339622641509</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U24" t="n">
-        <v>0.04528301886792455</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -32776,49 +32776,49 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5770491803278689</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H25" t="n">
-        <v>5.130491803278693</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I25" t="n">
-        <v>17.35344262295083</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J25" t="n">
-        <v>40.79737704918033</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K25" t="n">
-        <v>67.04262295081966</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L25" t="n">
-        <v>85.79147540983608</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M25" t="n">
-        <v>90.4550819672131</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N25" t="n">
-        <v>88.30426229508204</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O25" t="n">
-        <v>81.56327868852462</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P25" t="n">
-        <v>69.79147540983604</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q25" t="n">
-        <v>48.32000000000001</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R25" t="n">
-        <v>25.94622950819672</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S25" t="n">
-        <v>10.05639344262295</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T25" t="n">
-        <v>2.465573770491803</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U25" t="n">
-        <v>0.03147540983606562</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -32855,49 +32855,49 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>1.286432160804019</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H26" t="n">
-        <v>13.17467336683417</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I26" t="n">
-        <v>49.595175879397</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J26" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K26" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L26" t="n">
-        <v>203.0086432160805</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M26" t="n">
-        <v>225.8862311557789</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N26" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O26" t="n">
-        <v>216.7493467336684</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P26" t="n">
-        <v>184.9905527638191</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q26" t="n">
-        <v>138.9202010050251</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R26" t="n">
-        <v>80.80884422110556</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S26" t="n">
-        <v>29.31457286432162</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T26" t="n">
-        <v>5.631356783919597</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -32934,19 +32934,19 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.688301886792453</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H27" t="n">
-        <v>6.647547169811324</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I27" t="n">
-        <v>23.69811320754718</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J27" t="n">
-        <v>65.02943396226418</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K27" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L27" t="n">
         <v>138.5543797798742</v>
@@ -32961,22 +32961,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P27" t="n">
-        <v>131.4354716981132</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q27" t="n">
-        <v>87.86113207547173</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R27" t="n">
-        <v>42.73509433962267</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S27" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T27" t="n">
-        <v>2.774339622641509</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U27" t="n">
-        <v>0.04528301886792455</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -33013,49 +33013,49 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.5770491803278689</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H28" t="n">
-        <v>5.130491803278693</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I28" t="n">
-        <v>17.35344262295083</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J28" t="n">
-        <v>40.79737704918033</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K28" t="n">
-        <v>67.04262295081966</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L28" t="n">
-        <v>85.79147540983608</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M28" t="n">
-        <v>90.4550819672131</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N28" t="n">
-        <v>88.30426229508204</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O28" t="n">
-        <v>81.56327868852462</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P28" t="n">
-        <v>69.79147540983604</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q28" t="n">
-        <v>48.32000000000001</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R28" t="n">
-        <v>25.94622950819672</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S28" t="n">
-        <v>10.05639344262295</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T28" t="n">
-        <v>2.465573770491803</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U28" t="n">
-        <v>0.03147540983606562</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -33092,49 +33092,49 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>1.286432160804019</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H29" t="n">
-        <v>13.17467336683417</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I29" t="n">
-        <v>49.595175879397</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J29" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K29" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L29" t="n">
-        <v>203.0086432160805</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M29" t="n">
-        <v>225.8862311557789</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N29" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O29" t="n">
-        <v>216.7493467336684</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P29" t="n">
-        <v>184.9905527638191</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q29" t="n">
-        <v>138.9202010050251</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R29" t="n">
-        <v>80.80884422110556</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S29" t="n">
-        <v>29.31457286432162</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T29" t="n">
-        <v>5.631356783919597</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U29" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -33171,19 +33171,19 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.688301886792453</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H30" t="n">
-        <v>6.647547169811324</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I30" t="n">
-        <v>23.69811320754718</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J30" t="n">
-        <v>65.02943396226418</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K30" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L30" t="n">
         <v>138.5543797798742</v>
@@ -33198,22 +33198,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P30" t="n">
-        <v>131.4354716981132</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q30" t="n">
-        <v>87.86113207547173</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R30" t="n">
-        <v>42.73509433962267</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S30" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T30" t="n">
-        <v>2.774339622641509</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U30" t="n">
-        <v>0.04528301886792455</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -33250,49 +33250,49 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5770491803278689</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H31" t="n">
-        <v>5.130491803278693</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I31" t="n">
-        <v>17.35344262295083</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J31" t="n">
-        <v>40.79737704918033</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K31" t="n">
-        <v>67.04262295081966</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L31" t="n">
-        <v>85.79147540983608</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M31" t="n">
-        <v>90.4550819672131</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N31" t="n">
-        <v>88.30426229508204</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O31" t="n">
-        <v>81.56327868852462</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P31" t="n">
-        <v>69.79147540983605</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q31" t="n">
-        <v>48.32000000000001</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R31" t="n">
-        <v>25.94622950819672</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S31" t="n">
-        <v>10.05639344262295</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T31" t="n">
-        <v>2.465573770491803</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U31" t="n">
-        <v>0.03147540983606562</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -33329,49 +33329,49 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>1.286432160804019</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H32" t="n">
-        <v>13.17467336683416</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I32" t="n">
-        <v>49.595175879397</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J32" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K32" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L32" t="n">
-        <v>203.0086432160804</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M32" t="n">
-        <v>225.8862311557789</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N32" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O32" t="n">
-        <v>216.7493467336684</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P32" t="n">
-        <v>184.9905527638191</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q32" t="n">
-        <v>138.9202010050251</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R32" t="n">
-        <v>80.80884422110555</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S32" t="n">
-        <v>29.31457286432162</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T32" t="n">
-        <v>5.631356783919596</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U32" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -33408,19 +33408,19 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.6883018867924529</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H33" t="n">
-        <v>6.647547169811322</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I33" t="n">
-        <v>23.69811320754717</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J33" t="n">
-        <v>65.02943396226416</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K33" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L33" t="n">
         <v>138.5543797798742</v>
@@ -33435,22 +33435,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P33" t="n">
-        <v>131.4354716981132</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q33" t="n">
-        <v>87.86113207547172</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R33" t="n">
-        <v>42.73509433962266</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S33" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T33" t="n">
-        <v>2.774339622641508</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U33" t="n">
-        <v>0.04528301886792455</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -33487,49 +33487,49 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.5770491803278688</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H34" t="n">
-        <v>5.130491803278692</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I34" t="n">
-        <v>17.35344262295082</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J34" t="n">
-        <v>40.79737704918032</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K34" t="n">
-        <v>67.04262295081965</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L34" t="n">
-        <v>85.79147540983607</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M34" t="n">
-        <v>90.45508196721309</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N34" t="n">
-        <v>88.30426229508203</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O34" t="n">
-        <v>81.5632786885246</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P34" t="n">
-        <v>69.79147540983602</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q34" t="n">
-        <v>48.32</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R34" t="n">
-        <v>25.94622950819671</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S34" t="n">
-        <v>10.05639344262295</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T34" t="n">
-        <v>2.465573770491802</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U34" t="n">
-        <v>0.03147540983606561</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -33566,49 +33566,49 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>1.286432160804019</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H35" t="n">
-        <v>13.17467336683416</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I35" t="n">
-        <v>49.595175879397</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J35" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K35" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L35" t="n">
-        <v>203.0086432160804</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M35" t="n">
-        <v>225.8862311557789</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N35" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O35" t="n">
-        <v>216.7493467336684</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P35" t="n">
-        <v>184.9905527638191</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q35" t="n">
-        <v>138.9202010050251</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R35" t="n">
-        <v>80.80884422110555</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S35" t="n">
-        <v>29.31457286432162</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T35" t="n">
-        <v>5.631356783919596</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U35" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -33645,19 +33645,19 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.6883018867924529</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H36" t="n">
-        <v>6.647547169811322</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I36" t="n">
-        <v>23.69811320754717</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J36" t="n">
-        <v>65.02943396226416</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K36" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L36" t="n">
         <v>138.5543797798742</v>
@@ -33672,22 +33672,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P36" t="n">
-        <v>131.4354716981132</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q36" t="n">
-        <v>87.86113207547172</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R36" t="n">
-        <v>42.73509433962266</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S36" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T36" t="n">
-        <v>2.774339622641508</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U36" t="n">
-        <v>0.04528301886792455</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -33724,49 +33724,49 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.5770491803278688</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H37" t="n">
-        <v>5.130491803278692</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I37" t="n">
-        <v>17.35344262295082</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J37" t="n">
-        <v>40.79737704918032</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K37" t="n">
-        <v>67.04262295081965</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L37" t="n">
-        <v>85.79147540983607</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M37" t="n">
-        <v>90.45508196721309</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N37" t="n">
-        <v>88.30426229508203</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O37" t="n">
-        <v>81.5632786885246</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P37" t="n">
-        <v>69.79147540983602</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q37" t="n">
-        <v>48.32</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R37" t="n">
-        <v>25.94622950819671</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S37" t="n">
-        <v>10.05639344262295</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T37" t="n">
-        <v>2.465573770491802</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U37" t="n">
-        <v>0.03147540983606561</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -33803,49 +33803,49 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1.286432160804019</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H38" t="n">
-        <v>13.17467336683416</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I38" t="n">
-        <v>49.595175879397</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J38" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K38" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L38" t="n">
-        <v>203.0086432160804</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M38" t="n">
-        <v>225.8862311557789</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N38" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O38" t="n">
-        <v>216.7493467336684</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P38" t="n">
-        <v>184.9905527638191</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q38" t="n">
-        <v>138.9202010050251</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R38" t="n">
-        <v>80.80884422110555</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S38" t="n">
-        <v>29.31457286432162</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T38" t="n">
-        <v>5.631356783919596</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U38" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -33882,19 +33882,19 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.6883018867924529</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H39" t="n">
-        <v>6.647547169811322</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I39" t="n">
-        <v>23.69811320754717</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J39" t="n">
-        <v>65.02943396226416</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K39" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L39" t="n">
         <v>138.5543797798742</v>
@@ -33909,22 +33909,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P39" t="n">
-        <v>131.4354716981132</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q39" t="n">
-        <v>87.86113207547172</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R39" t="n">
-        <v>42.73509433962266</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S39" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T39" t="n">
-        <v>2.774339622641508</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U39" t="n">
-        <v>0.04528301886792455</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -33961,49 +33961,49 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.5770491803278688</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H40" t="n">
-        <v>5.130491803278692</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I40" t="n">
-        <v>17.35344262295082</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J40" t="n">
-        <v>40.79737704918032</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K40" t="n">
-        <v>67.04262295081965</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L40" t="n">
-        <v>85.79147540983607</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M40" t="n">
-        <v>90.45508196721309</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N40" t="n">
-        <v>88.30426229508203</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O40" t="n">
-        <v>81.5632786885246</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P40" t="n">
-        <v>69.79147540983602</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q40" t="n">
-        <v>48.32</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R40" t="n">
-        <v>25.94622950819671</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S40" t="n">
-        <v>10.05639344262295</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T40" t="n">
-        <v>2.465573770491802</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U40" t="n">
-        <v>0.03147540983606561</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -34040,49 +34040,49 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>1.286432160804019</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H41" t="n">
-        <v>13.17467336683416</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I41" t="n">
-        <v>49.595175879397</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J41" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K41" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L41" t="n">
-        <v>203.0086432160804</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M41" t="n">
-        <v>225.8862311557789</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N41" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O41" t="n">
-        <v>216.7493467336684</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P41" t="n">
-        <v>184.9905527638191</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q41" t="n">
-        <v>138.9202010050251</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R41" t="n">
-        <v>80.80884422110555</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S41" t="n">
-        <v>29.31457286432162</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T41" t="n">
-        <v>5.631356783919596</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U41" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -34119,19 +34119,19 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.6883018867924529</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H42" t="n">
-        <v>6.647547169811322</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I42" t="n">
-        <v>23.69811320754717</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J42" t="n">
-        <v>65.02943396226416</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K42" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L42" t="n">
         <v>138.5543797798742</v>
@@ -34146,22 +34146,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P42" t="n">
-        <v>131.4354716981132</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q42" t="n">
-        <v>87.86113207547172</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R42" t="n">
-        <v>42.73509433962266</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S42" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T42" t="n">
-        <v>2.774339622641508</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U42" t="n">
-        <v>0.04528301886792455</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -34198,49 +34198,49 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.5770491803278688</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H43" t="n">
-        <v>5.130491803278692</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I43" t="n">
-        <v>17.35344262295082</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J43" t="n">
-        <v>40.79737704918032</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K43" t="n">
-        <v>67.04262295081965</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L43" t="n">
-        <v>85.79147540983607</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M43" t="n">
-        <v>90.45508196721309</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N43" t="n">
-        <v>88.30426229508203</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O43" t="n">
-        <v>81.5632786885246</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P43" t="n">
-        <v>69.79147540983602</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q43" t="n">
-        <v>48.32</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R43" t="n">
-        <v>25.94622950819671</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S43" t="n">
-        <v>10.05639344262295</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T43" t="n">
-        <v>2.465573770491802</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U43" t="n">
-        <v>0.03147540983606561</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -34277,49 +34277,49 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>1.286432160804019</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H44" t="n">
-        <v>13.17467336683416</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I44" t="n">
-        <v>49.595175879397</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J44" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K44" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L44" t="n">
-        <v>203.0086432160804</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M44" t="n">
-        <v>225.8862311557789</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N44" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O44" t="n">
-        <v>216.7493467336684</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P44" t="n">
-        <v>184.9905527638191</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q44" t="n">
-        <v>138.9202010050251</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R44" t="n">
-        <v>80.80884422110555</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S44" t="n">
-        <v>29.31457286432162</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T44" t="n">
-        <v>5.631356783919596</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U44" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -34356,19 +34356,19 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.6883018867924529</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H45" t="n">
-        <v>6.647547169811322</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I45" t="n">
-        <v>23.69811320754717</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J45" t="n">
-        <v>65.02943396226416</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K45" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L45" t="n">
         <v>138.5543797798742</v>
@@ -34383,22 +34383,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P45" t="n">
-        <v>131.4354716981132</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q45" t="n">
-        <v>87.86113207547172</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R45" t="n">
-        <v>42.73509433962266</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S45" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T45" t="n">
-        <v>2.774339622641508</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U45" t="n">
-        <v>0.04528301886792455</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -34435,49 +34435,49 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.5770491803278688</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H46" t="n">
-        <v>5.130491803278692</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I46" t="n">
-        <v>17.35344262295082</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J46" t="n">
-        <v>40.79737704918032</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K46" t="n">
-        <v>67.04262295081965</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L46" t="n">
-        <v>85.79147540983607</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M46" t="n">
-        <v>90.45508196721309</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N46" t="n">
-        <v>88.30426229508203</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O46" t="n">
-        <v>81.5632786885246</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P46" t="n">
-        <v>69.79147540983602</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q46" t="n">
-        <v>48.32</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R46" t="n">
-        <v>25.94622950819671</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S46" t="n">
-        <v>10.05639344262295</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T46" t="n">
-        <v>2.465573770491802</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U46" t="n">
-        <v>0.03147540983606561</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
